--- a/data/2025/12-calarasi/92569-calarasi/budget_file.xlsx
+++ b/data/2025/12-calarasi/92569-calarasi/budget_file.xlsx
@@ -862,9 +862,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="3">
-        <f> salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</f>
-        <v/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>= salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -887,9 +888,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="3">
-        <f> cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</f>
-        <v/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>= cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1624,7 +1626,7 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'Venituri proprii' vs 'Sume primite de la UE/alti donatori in c'; 48.02 total_2026: parent 66.000,00 != sum(children) -1.747,00 (1 children); 48.02 trim1: parent 20.817,00 != sum(children) -1.747,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (18%): 'Venituri proprii' vs 'Sume primite de la UE/alti donatori in c'; 48.02 trim1: parent 20.817,00 != sum(children) -1.747,00 (1 children); 48.02 total_2026: parent 66.000,00 != sum(children) -1.747,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2664,7 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 8.650,00 != sum(children) 200,00 (1 children); 61.02 trim3: parent 2.180,00 != sum(children) 30,00 (1 children); 61.02 trim1: parent 2.180,00 != sum(children) 30,00 (1 children); 61.02 trim4: parent 2.010,00 != sum(children) 10,00 (1 children); 61.02 trim2: parent 2.280,00 != sum(children) 130,00 (1 children)</t>
+          <t>61.02 trim3: parent 2.180,00 != sum(children) 30,00 (1 children); 61.02 trim1: parent 2.180,00 != sum(children) 30,00 (1 children); 61.02 total_2026: parent 8.650,00 != sum(children) 200,00 (1 children); 61.02 trim2: parent 2.280,00 != sum(children) 130,00 (1 children); 61.02 trim4: parent 2.010,00 != sum(children) 10,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -7639,9 +7641,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="C168" s="3">
-        <f> salarii, sporuri, indemnizatii si alte drepturi salariale in bani si contributii aferente</f>
-        <v/>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>= salarii, sporuri, indemnizatii si alte drepturi salariale in bani si contributii aferente</t>
+        </is>
       </c>
       <c r="E168" t="n">
         <v>6</v>
@@ -7672,9 +7675,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="C169" s="3">
-        <f> cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</f>
-        <v/>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>= cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</t>
+        </is>
       </c>
       <c r="E169" t="n">
         <v>6</v>
@@ -7739,9 +7743,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="C171" s="3">
-        <f> salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</f>
-        <v/>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>= salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</t>
+        </is>
       </c>
       <c r="E171" t="n">
         <v>6</v>
@@ -7772,9 +7777,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="C172" s="3">
-        <f> cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</f>
-        <v/>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>= cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</t>
+        </is>
       </c>
       <c r="E172" t="n">
         <v>6</v>
@@ -7839,9 +7845,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="C174" s="3">
-        <f> salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</f>
-        <v/>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>= salarii ,sporuri,indemnizatii si alte drepturi salariale in bani si contributii aferente</t>
+        </is>
       </c>
       <c r="E174" t="n">
         <v>6</v>
@@ -7872,9 +7879,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="C175" s="3">
-        <f> cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</f>
-        <v/>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>= cheltuieli cu bunuri si servicii pentru intretinere curenta a unitatii de invatamant</t>
+        </is>
       </c>
       <c r="E175" t="n">
         <v>6</v>
@@ -8677,21 +8685,17 @@
       <c r="K193" s="7" t="n">
         <v>1680</v>
       </c>
-      <c r="L193" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="L193" s="7" t="n"/>
+      <c r="M193" s="7" t="n"/>
       <c r="N193" s="7" t="n"/>
       <c r="O193" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="P193" s="6" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 9.417,00 != sum(children) 350,00 (1 children); 67.02 trim2: parent 3.088,00 != sum(children) 350,00 (1 children); 67.02 total_2026: parent 9.417,00 != sum(children) 68,00 (2 children)</t>
+          <t>67.02 total_2026: parent 9.417,00 != sum(children) 350,00 (1 children); 67.02 trim2: parent 3.088,00 != sum(children) 350,00 (1 children); 67.02 total_2026: parent 9.417,00 != sum(children) 68,00 (2 children); 67.02 est2028: parent 0,00 != sum(children) 30,00 (2 children); 67.02 est2027: parent 0,00 != sum(children) 62,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -8989,16 +8993,12 @@
       <c r="K199" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L199" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="L199" s="7" t="n"/>
+      <c r="M199" s="7" t="n"/>
       <c r="N199" s="7" t="n"/>
       <c r="O199" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="P199" s="6" t="inlineStr">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="P383" s="6" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): 'Solutie de criptare si securizare mail F' vs 'Excedent'; 98.02 est2028: parent 98,00 != sum(children) 20,00 (1 children); 98.02 total_2026: parent 0,00 != sum(children) 20,00 (1 children); 98.02 est2027: parent 0,00 != sum(children) 20,00 (1 children); 98.02 est2029: parent 0,00 != sum(children) 10,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (16%): 'Solutie de criptare si securizare mail F' vs 'Excedent'; 98.02 est2029: parent 0,00 != sum(children) 10,00 (1 children); 98.02 total_2026: parent 0,00 != sum(children) 20,00 (1 children); 98.02 est2028: parent 98,00 != sum(children) 20,00 (1 children); 98.02 est2027: parent 0,00 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -18057,9 +18057,7 @@
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G432" s="7" t="n">
-        <v>20037</v>
-      </c>
+      <c r="G432" s="7" t="n"/>
       <c r="H432" s="7" t="n"/>
       <c r="I432" s="7" t="n">
         <v>10055</v>
@@ -18075,63 +18073,62 @@
       <c r="N432" s="7" t="n"/>
       <c r="O432" s="6" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="P432" s="6" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 0,00 != sum(children) 2.005,00 (1 children); 74.02 trim3: parent 930,00 != sum(children) 170,00 (1 children); 74.02 trim1: parent 0,00 != sum(children) 10.700,00 (1 children); 74.02 trim4: parent 678,00 != sum(children) 30,00 (1 children); 74.02 trim2: parent 10.055,00 != sum(children) 1.105,00 (1 children); cell re-read from image (unverified transcription)</t>
+          <t>unparseable cell '20.037 18.862' in column total_2026; 74.02 trim3: parent 930,00 != sum(children) 170,00 (1 children); 74.02 trim1: parent 0,00 != sum(children) 10.700,00 (1 children); 74.02 total_2026: parent 0,00 != sum(children) 2.005,00 (1 children); 74.02 trim2: parent 10.055,00 != sum(children) 1.105,00 (1 children); 74.02 trim4: parent 678,00 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
+      <c r="A433" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B433" s="6" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
+      <c r="C433" s="6" t="inlineStr">
         <is>
           <t>cheltuieli cu bunuri si servici</t>
         </is>
       </c>
-      <c r="E433" t="n">
+      <c r="D433" s="6" t="n"/>
+      <c r="E433" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F433" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G433" s="2" t="n"/>
-      <c r="H433" s="2" t="n">
-        <v>8364</v>
-      </c>
-      <c r="I433" s="2" t="n">
+      <c r="G433" s="7" t="n"/>
+      <c r="H433" s="7" t="n"/>
+      <c r="I433" s="7" t="n">
         <v>8935</v>
       </c>
-      <c r="J433" s="2" t="n">
+      <c r="J433" s="7" t="n">
         <v>885</v>
       </c>
-      <c r="K433" s="2" t="n">
+      <c r="K433" s="7" t="n">
         <v>678</v>
       </c>
-      <c r="L433" s="2" t="n"/>
-      <c r="M433" s="2" t="n"/>
-      <c r="N433" s="2" t="n"/>
-      <c r="O433" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P433" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="L433" s="7" t="n"/>
+      <c r="M433" s="7" t="n"/>
+      <c r="N433" s="7" t="n"/>
+      <c r="O433" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P433" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '8.374 8.364' in column trim1</t>
         </is>
       </c>
     </row>
@@ -18237,50 +18234,50 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
+      <c r="A437" s="6" t="inlineStr">
         <is>
           <t>74.02.05.02</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="B437" s="6" t="n"/>
+      <c r="C437" s="6" t="inlineStr">
         <is>
           <t>de rulare a transportului public local (strada Bucuresti) Colectarea,tratarea si distrugerea deseurilor</t>
         </is>
       </c>
-      <c r="E437" t="n">
+      <c r="D437" s="6" t="n"/>
+      <c r="E437" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F437" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <t>expense_functional</t>
         </is>
       </c>
-      <c r="G437" s="2" t="n">
-        <v>17022</v>
-      </c>
-      <c r="H437" s="2" t="n">
+      <c r="G437" s="7" t="n"/>
+      <c r="H437" s="7" t="n">
         <v>7664</v>
       </c>
-      <c r="I437" s="2" t="n">
+      <c r="I437" s="7" t="n">
         <v>7950</v>
       </c>
-      <c r="J437" s="2" t="n">
+      <c r="J437" s="7" t="n">
         <v>760</v>
       </c>
-      <c r="K437" s="2" t="n">
+      <c r="K437" s="7" t="n">
         <v>648</v>
       </c>
-      <c r="L437" s="2" t="n"/>
-      <c r="M437" s="2" t="n"/>
-      <c r="N437" s="2" t="n"/>
-      <c r="O437" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
-        </is>
-      </c>
-      <c r="P437" t="inlineStr">
-        <is>
-          <t>cell re-read from image (unverified transcription)</t>
+      <c r="L437" s="7" t="n"/>
+      <c r="M437" s="7" t="n"/>
+      <c r="N437" s="7" t="n"/>
+      <c r="O437" s="6" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="P437" s="6" t="inlineStr">
+        <is>
+          <t>unparseable cell '1.000 17.022' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -19226,7 +19223,7 @@
       </c>
       <c r="P463" s="6" t="inlineStr">
         <is>
-          <t>84.02 est2028: parent 0,00 != sum(children) 110,00 (2 children); 84.02 total_2026: parent 32.673,00 != sum(children) 20,00 (2 children); 84.02 est2027: parent 0,00 != sum(children) 10,00 (2 children); 84.02 est2029: parent 0,00 != sum(children) 20,00 (2 children)</t>
+          <t>84.02 est2029: parent 0,00 != sum(children) 20,00 (2 children); 84.02 total_2026: parent 32.673,00 != sum(children) 20,00 (2 children); 84.02 est2028: parent 0,00 != sum(children) 110,00 (2 children); 84.02 est2027: parent 0,00 != sum(children) 10,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -21832,7 +21829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F367"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21878,7 +21875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -21887,28 +21884,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 48.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'Subventii-supliment incalzire' vs 'Subventii pentru acordarea ajutorului pe'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -21921,24 +21913,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>48.02.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 48.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume alocate din bugetul UE pentru proie' vs 'Fondul European de Dezvoltare Regională '</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -21951,29 +21938,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 54.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (18%): 'Venituri proprii' vs 'Sume primite de la UE/alti donatori in c'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -21981,29 +21963,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 54.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>48.02 trim1: parent 20.817,00 != sum(children) -1.747,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -22011,7 +21993,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>48.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -22021,14 +22003,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>48.02 total_2026: parent 66.000,00 != sum(children) -1.747,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -22041,24 +22023,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>40.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (32%): 'Sume din excedentul bugetar al anului 20' vs 'Prime acordate producătorilor agricoli'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -22071,24 +22048,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (41%): 'Sume din excedentul bugetar al anului 20' vs 'Susţinerea exportului, a mediului de afa'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22101,24 +22073,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>51.02.01.03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (53%): 'AUTORITATE PUBLICA SI ACTIUNI EXTERNE' vs 'Autoritati executive'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -22131,114 +22098,104 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>51.59.44</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02 est2027: sum now consistent — applied</t>
+          <t>code 51.59.44 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02 est2028: sum now consistent — applied</t>
+          <t>54.02 total_2026: parent 4.860,00 != sum(children) 2.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>54.02 trim4: parent 2.534,00 != sum(children) 2.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -22247,28 +22204,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (30%): 'cheltuieli de capital -dotari' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -22277,28 +22229,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>67.02.05</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02.05 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (30%): 'cotizatii organisme' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -22307,28 +22254,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.02.05</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 67.02.05 trim2: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -22337,28 +22279,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'cheltuieli alegeri' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -22367,28 +22304,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 trim1: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'S.P.Evidenta persoanelor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -22397,28 +22329,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 trim2: still inconsistent — UNRESOLVED</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -22427,128 +22354,148 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 trim3: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (30%): 'Implementarea Strategiei pentru Integrit' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>trim4</t>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 74.02 trim4: still inconsistent — UNRESOLVED</t>
+          <t>61.02 trim3: parent 2.180,00 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>trim1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p5: 0 cells recovered</t>
+          <t>61.02 trim1: parent 2.180,00 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total_2026</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p14: 3 cells recovered</t>
+          <t>61.02 total_2026: parent 8.650,00 != sum(children) 200,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>42.02.34</t>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'Subventii-supliment incalzire' vs 'Subventii pentru acordarea ajutorului pe'</t>
+          <t>61.02 trim2: parent 2.280,00 != sum(children) 130,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -22556,12 +22503,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.02.01</t>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume alocate din bugetul UE pentru proie' vs 'Fondul European de Dezvoltare Regională '</t>
+          <t>61.02 trim4: parent 2.010,00 != sum(children) 10,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -22581,24 +22533,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'Venituri proprii' vs 'Sume primite de la UE/alti donatori in c'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -22606,29 +22558,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>48.02 total_2026: parent 66.000,00 != sum(children) -1.747,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (29%): 'cheltuieli de capital-sirena electronica' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -22636,17 +22583,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.02 trim1: parent 20.817,00 != sum(children) -1.747,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (35%): 'salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -22662,16 +22604,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>40.11</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Sume din excedentul bugetar al anului 20' vs 'Prime acordate producătorilor agricoli'</t>
+          <t>name mismatch vs nomenclator (38%): 'proiecte finantate prin PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
@@ -22687,16 +22629,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'Sume din excedentul bugetar al anului 20' vs 'Susţinerea exportului, a mediului de afa'</t>
+          <t>name mismatch vs nomenclator (42%): 'proiecte finantate prin PNRR' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
@@ -22712,16 +22654,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.02.01.03</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (53%): 'AUTORITATE PUBLICA SI ACTIUNI EXTERNE' vs 'Autoritati executive'</t>
+          <t>name mismatch vs nomenclator (30%): '- cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -22737,108 +22679,98 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (34%): 'Gradinita cu program prelungit nr.1 Tara' vs 'Învatamânt prescolar'</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51.59.44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>code 51.59.44 (expense_functional) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>54.02 total_2026: parent 4.860,00 != sum(children) 2.000,00 (1 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54.02 trim4: parent 2.534,00 != sum(children) 2.000,00 (1 children)</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22847,48 +22779,48 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'cheltuieli de capital -dotari' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65.02.00.01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'cotizatii organisme' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>code 65.02.00.01 (expense_functional) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22897,23 +22829,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22922,23 +22854,23 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'cheltuieli alegeri' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22947,16 +22879,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'S.P.Evidenta persoanelor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
@@ -22972,11 +22904,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -22997,166 +22929,141 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Implementarea Strategiei pentru Integrit' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 8.650,00 != sum(children) 200,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.3 Amic' vs 'Învatamânt prescolar'</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.02 trim3: parent 2.180,00 != sum(children) 30,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.02 trim1: parent 2.180,00 != sum(children) 30,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.02 trim4: parent 2.010,00 != sum(children) 10,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.02 trim2: parent 2.280,00 != sum(children) 130,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.4 Step' vs 'Învatamânt prescolar'</t>
         </is>
       </c>
     </row>
@@ -23172,16 +23079,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23104,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -23206,7 +23113,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'cheltuieli de capital-sirena electronica' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -23222,23 +23129,23 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.5 Aric' vs 'Învatamânt prescolar'</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -23251,12 +23158,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'proiecte finantate prin PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23276,12 +23183,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'proiecte finantate prin PNRR' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>name mismatch vs nomenclator (29%): 'Gimnaziul Carol I' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
@@ -23301,19 +23208,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): '- cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23326,19 +23233,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Gradinita cu program prelungit nr.1 Tara' vs 'Învatamânt prescolar'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -23351,12 +23258,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23376,19 +23283,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23401,19 +23308,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -23426,24 +23333,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'Scoala gimnaziala nr.5 Nicolae Titulescu' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -23451,12 +23358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>65.02.00.01</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>code 65.02.00.01 (expense_functional) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23501,19 +23408,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -23522,23 +23429,23 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -23547,23 +23454,23 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>duplicate of p2 with different values</t>
+          <t>name mismatch vs nomenclator (35%): 'Scoala gimnaziala nr.8 Mircea Voda' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -23572,16 +23479,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23597,23 +23504,23 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.3 Amic' vs 'Învatamânt prescolar'</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -23622,7 +23529,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -23631,14 +23538,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -23647,16 +23554,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23672,11 +23579,11 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -23697,7 +23604,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -23706,14 +23613,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.4 Step' vs 'Învatamânt prescolar'</t>
+          <t>name mismatch vs nomenclator (34%): 'Gradinita cu program prelungit nr.9 Voin' vs 'Învatamânt prescolar'</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -23722,23 +23629,23 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.03.01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -23747,16 +23654,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23772,16 +23679,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Gradinita cu program prelungit nr.5 Aric' vs 'Învatamânt prescolar'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -23797,11 +23704,11 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -23822,7 +23729,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -23831,14 +23738,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Gimnaziul Carol I' vs 'Învatamânt primar'</t>
+          <t>name mismatch vs nomenclator (39%): 'Scoala gimnaziala nr.9 Constantin Branco' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -23847,23 +23754,23 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -23872,7 +23779,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -23881,7 +23788,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -23897,11 +23804,11 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -23922,11 +23829,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -23938,7 +23845,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -23947,16 +23854,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -23972,23 +23879,23 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Scoala gimnaziala nr.5 Nicolae Titulescu' vs 'Învatamânt primar'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -23997,7 +23904,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -24006,14 +23913,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Scoala cu clasele I-VIII Mihai Viteazul' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -24022,23 +23929,23 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -24047,23 +23954,23 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -24076,19 +23983,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -24101,12 +24008,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Scoala gimnaziala nr.8 Mircea Voda' vs 'Învatamânt primar'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -24126,7 +24033,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -24151,19 +24058,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -24176,12 +24083,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (37%): 'Scoala gimnaziala nr.11 Tudor Vladimires' vs 'Învatamânt primar'</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24108,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65.02.03.02</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -24213,7 +24120,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -24226,19 +24133,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -24251,12 +24158,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Gradinita cu program prelungit nr.9 Voin' vs 'Învatamânt prescolar'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -24276,19 +24183,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>65.02.03.01</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -24301,12 +24208,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -24326,19 +24233,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): 'Liceul Agricol Sandu Aldea' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -24351,19 +24258,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -24376,12 +24283,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Scoala gimnaziala nr.9 Constantin Branco' vs 'Învatamânt primar'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -24401,7 +24308,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -24422,16 +24329,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (35%): 'Liceul tenologic transportuti AUTO' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
@@ -24447,23 +24354,23 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -24472,16 +24379,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -24497,11 +24404,11 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -24513,7 +24420,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -24522,48 +24429,48 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>65.02.03.02</t>
+        <v>5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Scoala cu clasele I-VIII Mihai Viteazul' vs 'Învatamânt primar'</t>
+          <t>unparseable cell 'L' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -24572,16 +24479,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -24597,16 +24504,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (30%): 'Colegiul tehnic Stefan Banulescu' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
@@ -24622,11 +24529,11 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -24638,7 +24545,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -24647,23 +24554,23 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (33%): 'burse elevi' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -24672,16 +24579,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -24697,23 +24604,23 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (23%): 'Liceul Danubius' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -24722,23 +24629,23 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Scoala gimnaziala nr.11 Tudor Vladimires' vs 'Învatamânt primar'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -24747,23 +24654,23 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>65.02.03.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -24772,7 +24679,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -24781,7 +24688,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -24797,7 +24704,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -24822,7 +24729,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -24831,7 +24738,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -24847,7 +24754,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -24872,7 +24779,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -24881,14 +24788,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'Liceul Agricol Sandu Aldea' vs 'Învatamânt secundar superior'</t>
+          <t>name mismatch vs nomenclator (27%): 'Colegiul Economic' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -24897,23 +24804,23 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -24922,7 +24829,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24931,7 +24838,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -24947,7 +24854,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -24963,7 +24870,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -24976,19 +24883,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Liceul tenologic transportuti AUTO' vs 'Învatamânt secundar superior'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -25001,19 +24908,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -25026,19 +24933,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -25051,12 +24958,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (34%): 'Liceul teoretic Mihai Eminescu' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
@@ -25076,44 +24983,44 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>5</v>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>unparseable cell 'L' in column total_2026</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -25126,19 +25033,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -25151,12 +25058,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Colegiul tehnic Stefan Banulescu' vs 'Învatamânt secundar superior'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -25201,19 +25108,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'burse elevi' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -25231,7 +25138,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -25256,7 +25163,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Liceul Danubius' vs 'Învatamânt secundar superior'</t>
+          <t>name mismatch vs nomenclator (34%): 'Colegiul National Barbu Stirbei' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25195,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -25301,12 +25208,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -25326,7 +25233,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -25338,7 +25245,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -25351,12 +25258,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -25376,7 +25283,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -25401,19 +25308,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>65.02.04.02</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (42%): 'Grup scolar Dan Mateescu' vs 'Învatamânt secundar superior'</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -25431,14 +25338,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Colegiul Economic' vs 'Învatamânt secundar superior'</t>
+          <t>duplicate of p4 with different values</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -25451,19 +25358,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -25481,7 +25388,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -25597,23 +25504,23 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Liceul teoretic Mihai Eminescu' vs 'Învatamânt secundar superior'</t>
+          <t>name mismatch vs nomenclator (32%): 'Invatamant particular sau confesional TO' vs 'TITLUL VII ALTE TRANSFERURI'</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -25622,16 +25529,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI IN DOMENIUL INVATAMANTUL' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -25647,23 +25554,23 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (38%): 'proiecte finantate prin PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -25672,23 +25579,23 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (42%): 'proiecte finantate prin PNRR' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -25697,23 +25604,23 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>66.02.50.50</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (51%): 'Alte cheltuieli cu sanatatea P.M.C.' vs 'Alte institutii si actiuni sanitare'</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -25722,7 +25629,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -25731,7 +25638,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'P.M.C.-transport donatori sange+alte per' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
         </is>
       </c>
     </row>
@@ -25747,141 +25654,166 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (48%): 'Titlul I salarii asistenti scolari si co' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>67.02 total_2026: parent 9.417,00 != sum(children) 350,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Colegiul National Barbu Stirbei' vs 'Învatamânt secundar superior'</t>
+          <t>67.02 trim2: parent 3.088,00 != sum(children) 350,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>67.02 total_2026: parent 9.417,00 != sum(children) 68,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>67.02 est2028: parent 0,00 != sum(children) 30,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>67.02 est2027: parent 0,00 != sum(children) 62,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -25897,16 +25829,16 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
@@ -25922,16 +25854,16 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -25947,73 +25879,83 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Grup scolar Dan Mateescu' vs 'Învatamânt secundar superior'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>65.02.04.02</t>
+          <t>67.02.05</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>duplicate of p4 with different values</t>
+          <t>67.02.05 total_2026: parent 350,00 != sum(children) 50,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67.02.05</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '- salarii si asimilate' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>67.02.05 trim2: parent 350,00 != sum(children) 50,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -26022,23 +25964,23 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (8%): 'Finantari nerambursabile din fonduri pub' vs 'Sport'</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -26047,16 +25989,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (8%): 'Finantari nerambursabile din fonduri pub' vs 'Sport'</t>
         </is>
       </c>
     </row>
@@ -26072,16 +26014,16 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -26097,23 +26039,23 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (47%): 'sume aferente persoanelor cu handicap ne' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -26122,23 +26064,23 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Avize punere in valoare si depozitat mat' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -26147,16 +26089,16 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Invatamant particular sau confesional TO' vs 'TITLUL VII ALTE TRANSFERURI'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -26172,16 +26114,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'ALTE CHELTUIELI IN DOMENIUL INVATAMANTUL' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (32%): 'Intretinere foisoare' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
@@ -26197,23 +26139,23 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'proiecte finantate prin PNRR' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>name mismatch vs nomenclator (29%): 'Placute de informare /avertizare ,platfo' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -26222,16 +26164,16 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'proiecte finantate prin PNRR' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -26247,16 +26189,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>66.02.50.50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (51%): 'Alte cheltuieli cu sanatatea P.M.C.' vs 'Alte institutii si actiuni sanitare'</t>
+          <t>name mismatch vs nomenclator (26%): 'Reparatii/intretinere mobilier stradal' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
@@ -26272,23 +26214,23 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'P.M.C.-transport donatori sange+alte per' vs 'TITLUL IX  ASISTENTA SOCIALA'</t>
+          <t>name mismatch vs nomenclator (29%): 'Servicii de vopsitorie mobilier urban' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -26297,106 +26239,91 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (48%): 'Titlul I salarii asistenti scolari si co' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 9.417,00 != sum(children) 350,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (37%): 'Achizitionare/intretinere si reparatii p' vs 'Partea a III-a CHELTUIELI SOCIAL-CULTURA'</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>67.02 trim2: parent 3.088,00 != sum(children) 350,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (26%): 'Imprejmuire cu gard protectie Cinematogr' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>67.02 total_2026: parent 9.417,00 != sum(children) 68,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (37%): 'Servicii consultanta in domeniul achizit' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
@@ -26412,23 +26339,23 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (45%): 'Lucrari de scoatere a cioatelor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -26437,16 +26364,16 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Achizitionare si montare panouri de afis' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
         </is>
       </c>
     </row>
@@ -26462,76 +26389,66 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (27%): 'Construire baza sportiva TIP 1, str. Ale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>67.02.05</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>67.02.05 total_2026: parent 350,00 != sum(children) 50,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (24%): 'Serviciul municipal pentru promovarea pa' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>67.02.05</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>67.02.05 trim2: parent 350,00 != sum(children) 50,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (24%): '28 Martie Ora Pamantului' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
@@ -26547,23 +26464,23 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (8%): 'Finantari nerambursabile din fonduri pub' vs 'Sport'</t>
+          <t>name mismatch vs nomenclator (34%): '9 Mai Ziua Independentei Romaniei si Ziu' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -26572,23 +26489,23 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (8%): 'Finantari nerambursabile din fonduri pub' vs 'Sport'</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -26597,16 +26514,16 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (31%): '1 Iunie Ziua Internationala a Copilului' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
@@ -26622,23 +26539,23 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (47%): 'sume aferente persoanelor cu handicap ne' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>name mismatch vs nomenclator (29%): '15 august-Ziua Marinei' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -26647,23 +26564,23 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Avize punere in valoare si depozitat mat' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -26672,23 +26589,23 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Zilele Municipiului Calarasi,inclusiv Nu' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -26697,16 +26614,16 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Intretinere foisoare' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -26722,16 +26639,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Placute de informare /avertizare ,platfo' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (42%): '29 Iunie Ziua DUNARII' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -26747,16 +26664,16 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -26772,23 +26689,23 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Reparatii/intretinere mobilier stradal' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>name mismatch vs nomenclator (38%): '25 octombrie Ziua Armatei Romane' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -26797,23 +26714,23 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Servicii de vopsitorie mobilier urban' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -26822,23 +26739,23 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (36%): '1 Decembrie Ziua Nationala a Romaniei' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -26847,16 +26764,16 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Achizitionare/intretinere si reparatii p' vs 'Partea a III-a CHELTUIELI SOCIAL-CULTURA'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -26872,23 +26789,23 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Imprejmuire cu gard protectie Cinematogr' vs 'TITLUL III DOBANZI'</t>
+          <t>name mismatch vs nomenclator (37%): '22 Decembrie-Ziua Revolutiei' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -26897,16 +26814,16 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Servicii consultanta in domeniul achizit' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -26922,16 +26839,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (45%): 'Lucrari de scoatere a cioatelor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (21%): 'Servicii muzica fanfara si muzica estrad' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
         </is>
       </c>
     </row>
@@ -26947,16 +26864,16 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Achizitionare si montare panouri de afis' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
+          <t>name mismatch vs nomenclator (39%): 'Alte evenimente si servicii' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
@@ -26972,23 +26889,23 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Construire baza sportiva TIP 1, str. Ale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (24%): 'capital' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -26997,7 +26914,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -27006,7 +26923,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Serviciul municipal pentru promovarea pa' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -27026,19 +26943,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): '28 Martie Ora Pamantului' vs 'Taxe pe servicii specifice'</t>
+          <t>name mismatch vs nomenclator (31%): 'Reabilitare,modernizare,extindere si dot' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -27051,19 +26968,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): '9 Mai Ziua Independentei Romaniei si Ziu' vs 'Taxe pe servicii specifice'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -27076,19 +26993,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -27101,12 +27018,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): '1 Iunie Ziua Internationala a Copilului' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -27126,19 +27043,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): '15 august-Ziua Marinei' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (38%): 'cheltuieli de capital' vs 'TITLUL VII ALTE TRANSFERURI'</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -27151,12 +27068,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (24%): 'cheltuieli de capital' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -27172,7 +27089,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27181,7 +27098,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Zilele Municipiului Calarasi,inclusiv Nu' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (34%): 'supliment energie pentru consum combusti' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -27197,7 +27114,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -27222,23 +27139,23 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): '29 Iunie Ziua DUNARII' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (34%): 'cheltuieli de capital' vs 'Alte operaţiuni financiare'</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -27247,48 +27164,48 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (40%): 'cheltuieli de capital' vs 'Alte impozite si taxe fiscale'</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>8</v>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>10</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): '25 octombrie Ziua Armatei Romane' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell '0L' in column est2028</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -27297,7 +27214,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -27306,14 +27223,14 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (20%): 'Taxe OCPI' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -27322,23 +27239,23 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): '1 Decembrie Ziua Nationala a Romaniei' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -27347,23 +27264,23 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (19%): 'Taxe,avize,acorduri' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -27372,23 +27289,23 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): '22 Decembrie-Ziua Revolutiei' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -27397,23 +27314,23 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (44%): 'Servicii tehnice(dezmembrari,apartamenta' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -27422,23 +27339,23 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'Servicii muzica fanfara si muzica estrad' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -27447,16 +27364,16 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Alte evenimente si servicii' vs 'TITLUL IV SUBVENTII'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -27472,16 +27389,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'capital' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (44%): 'Servicii suport tehnic intocmire documen' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -27497,11 +27414,11 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -27522,16 +27439,16 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Reabilitare,modernizare,extindere si dot' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (32%): 'Lucrări de înregistrare sistematică pe s' vs 'Cultura, recreere si religie'</t>
         </is>
       </c>
     </row>
@@ -27547,16 +27464,16 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -27572,16 +27489,16 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (29%): 'Taxe notariale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -27597,16 +27514,16 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -27622,16 +27539,16 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'cheltuieli de capital' vs 'TITLUL VII ALTE TRANSFERURI'</t>
+          <t>name mismatch vs nomenclator (19%): 'Actualizarea Registrului Spatii Verzi Se' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
@@ -27647,23 +27564,23 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'cheltuieli de capital' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (24%): 'Centrului de zi pentru persoane adulte c' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -27672,23 +27589,23 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'supliment energie pentru consum combusti' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -27697,23 +27614,23 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (39%): 'Servicii evaluari, reevaluari si actuali' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -27722,16 +27639,16 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'cheltuieli de capital' vs 'Alte operaţiuni financiare'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -27747,41 +27664,41 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'cheltuieli de capital' vs 'Alte impozite si taxe fiscale'</t>
+          <t>name mismatch vs nomenclator (31%): 'Elaborare PUZ "Construire locuinte tiner' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>10</v>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>est2028</t>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>35.02</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>unparseable cell '0L' in column est2028</t>
+          <t>name mismatch vs nomenclator (26%): 'Servicii asistenta tehnica din partea pr' vs 'Amenzi, penalitati si confiscari'</t>
         </is>
       </c>
     </row>
@@ -27797,7 +27714,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27806,7 +27723,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (20%): 'Taxe OCPI' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (28%): 'Servicii ridicare garaje si desfiintare ' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27739,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27831,7 +27748,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -27847,23 +27764,23 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Taxe,avize,acorduri' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>name mismatch vs nomenclator (31%): 'Servicii de coordonare in materie de sec' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -27872,23 +27789,23 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>name mismatch vs nomenclator (23%): 'Demolare cos de fum aferent obiectivului' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -27897,23 +27814,23 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'Servicii tehnice(dezmembrari,apartamenta' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -27922,23 +27839,23 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (34%): 'Reparatii curente subsol Gradinita Amici' vs 'TITLUL XVIII FONDUL NATIONAL DE DEZVOLTA'</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -27947,23 +27864,23 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Montare numere administrative si placute' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -27972,23 +27889,23 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'Servicii suport tehnic intocmire documen' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -27997,16 +27914,16 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (31%): 'Intretinere si igienizare arhiva PMC str' vs 'TITLUL XXIII REZERVE, EXCEDENT/DEFICIT'</t>
         </is>
       </c>
     </row>
@@ -28022,16 +27939,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Lucrări de înregistrare sistematică pe s' vs 'Cultura, recreere si religie'</t>
+          <t>name mismatch vs nomenclator (32%): 'Lucrari complementare luminator sediul P' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -28047,48 +27964,48 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>10</v>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>20</t>
+        <v>11</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Taxe notariale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>unparseable cell '0L' in column est2028</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -28097,23 +28014,23 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Cr o  al Gl Gl   G GurB (PNRR) Cresterea' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -28122,16 +28039,16 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'Actualizarea Registrului Spatii Verzi Se' vs 'TITLUL IV SUBVENTII'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -28147,16 +28064,16 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Centrului de zi pentru persoane adulte c' vs 'TITLUL III DOBANZI'</t>
+          <t>name mismatch vs nomenclator (19%): 'C1,C2,C3 (PNRR)' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -28172,16 +28089,16 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -28197,16 +28114,16 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Servicii evaluari, reevaluari si actuali' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (27%): 'Cresterea eficientei energetice a Scolii' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -28222,16 +28139,16 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -28247,7 +28164,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28256,14 +28173,14 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Elaborare PUZ "Construire locuinte tiner' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (24%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -28272,16 +28189,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): 'Servicii asistenta tehnica din partea pr' vs 'Amenzi, penalitati si confiscari'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -28301,12 +28218,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Servicii ridicare garaje si desfiintare ' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (21%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -28326,12 +28243,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -28351,19 +28268,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Servicii de coordonare in materie de sec' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
+          <t>name mismatch vs nomenclator (42%): 'Construirea de locuințe nzeb plus pentru' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -28376,19 +28293,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (23%): 'Demolare cos de fum aferent obiectivului' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -28401,19 +28318,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'Infiintare si colectare centru de colect' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -28426,12 +28343,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'Reparatii curente subsol Gradinita Amici' vs 'TITLUL XVIII FONDUL NATIONAL DE DEZVOLTA'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28451,12 +28368,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Montare numere administrative si placute' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (32%): 'Sistem de management inteligent al infor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -28476,12 +28393,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28497,23 +28414,23 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Intretinere si igienizare arhiva PMC str' vs 'TITLUL XXIII REZERVE, EXCEDENT/DEFICIT'</t>
+          <t>name mismatch vs nomenclator (25%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -28522,23 +28439,23 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Lucrari complementare luminator sediul P' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -28547,16 +28464,16 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -28566,22 +28483,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B263" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>11</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>est2028</t>
+        <v>12</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>unparseable cell '0L' in column est2028</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28597,7 +28514,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28606,7 +28523,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'Cr o  al Gl Gl   G GurB (PNRR) Cresterea' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (30%): 'Inlocuire centrala termica si modificare' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
@@ -28622,7 +28539,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -28647,16 +28564,16 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (19%): 'C1,C2,C3 (PNRR)' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (46%): 'Achizitie si montaj instalatie incalzire' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -28672,16 +28589,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28697,16 +28614,16 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Cresterea eficientei energetice a Scolii' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (25%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -28722,16 +28639,16 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -28747,16 +28664,16 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (21%): 'Modernizarea si dotarea Centrului de zi ' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
@@ -28772,16 +28689,16 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -28797,123 +28714,143 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>98.02</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (16%): 'Solutie de criptare si securizare mail F' vs 'Excedent'</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>98.02</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>98.02 est2029: parent 0,00 != sum(children) 10,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>98.02</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (42%): 'Construirea de locuințe nzeb plus pentru' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>98.02 total_2026: parent 0,00 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>98.02</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>98.02 est2028: parent 98,00 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>98.02</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Infiintare si colectare centru de colect' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>98.02 est2027: parent 0,00 != sum(children) 20,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -28922,16 +28859,16 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (44%): 'Extindere supraveghere video intrere Slo' vs 'Venituri din prestari de servicii si alt'</t>
         </is>
       </c>
     </row>
@@ -28947,23 +28884,23 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Sistem de management inteligent al infor' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (33%): 'Instalare Camere Volna+ analiza de risc' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -28972,16 +28909,16 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (41%): 'Instalare Punct distributie Directia Agr' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
         </is>
       </c>
     </row>
@@ -28997,23 +28934,23 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (32%): 'Instalare camere pietonal' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -29022,16 +28959,16 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (37%): 'Servicii dirigentie de santier pentru in' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
         </is>
       </c>
     </row>
@@ -29047,23 +28984,23 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (27%): 'Intretinere semafoare' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -29072,16 +29009,16 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (29%): 'Spor de putere scoala nr. 11 Tudor Vladi' vs 'Asigurari si asistenta sociala'</t>
         </is>
       </c>
     </row>
@@ -29097,16 +29034,16 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>98.02</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Inlocuire centrala termica si modificare' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (12%): 'Reparatii retea iluminat public b-dul 1 ' vs 'Excedent'</t>
         </is>
       </c>
     </row>
@@ -29122,16 +29059,16 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>98.02</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>duplicate of p12 with different values</t>
         </is>
       </c>
     </row>
@@ -29147,16 +29084,16 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (46%): 'Achizitie si montaj instalatie incalzire' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (24%): 'Iluminat public in parcări nou infiintat' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
@@ -29172,16 +29109,16 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>duplicate of p13 with different values</t>
         </is>
       </c>
     </row>
@@ -29197,16 +29134,16 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Renovare energetica moderata a cladirilo' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (35%): 'cheltuieli de capital din care:' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29216,97 +29153,112 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>12</v>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>14</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>unparseable cell '20.037 18.862' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>trim3</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'Modernizarea si dotarea Centrului de zi ' vs 'TITLUL III DOBANZI'</t>
+          <t>74.02 trim3: parent 930,00 != sum(children) 170,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>74.02 trim1: parent 0,00 != sum(children) 10.700,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (16%): 'Solutie de criptare si securizare mail F' vs 'Excedent'</t>
+          <t>74.02 total_2026: parent 0,00 != sum(children) 2.005,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -29322,21 +29274,21 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>est2028</t>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>98.02 est2028: parent 98,00 != sum(children) 20,00 (1 children)</t>
+          <t>74.02 trim2: parent 10.055,00 != sum(children) 1.105,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -29352,28 +29304,28 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>total_2026</t>
+          <t>trim4</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>98.02 total_2026: parent 0,00 != sum(children) 20,00 (1 children)</t>
+          <t>74.02 trim4: parent 678,00 != sum(children) 30,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
@@ -29382,28 +29334,23 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>12</v>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>98.02</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>est2027</t>
+          <t>trim1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>98.02 est2027: parent 0,00 != sum(children) 20,00 (1 children)</t>
+          <t>unparseable cell '8.374 8.364' in column trim1</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
@@ -29412,21 +29359,16 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>12</v>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>98.02</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>est2029</t>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>98.02 est2029: parent 0,00 != sum(children) 10,00 (1 children)</t>
+          <t>unparseable cell '1.000 17.022' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -29442,16 +29384,16 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'Extindere supraveghere video intrere Slo' vs 'Venituri din prestari de servicii si alt'</t>
+          <t>name mismatch vs nomenclator (34%): 'cheltuieli de capital, din care:' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29467,116 +29409,136 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'Instalare Camere Volna+ analiza de risc' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>name mismatch vs nomenclator (35%): 'ENERGIE TERMICA' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>est2029</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'Instalare Punct distributie Directia Agr' vs 'Titlul XIII „Proiecte cu finanțare din s'</t>
+          <t>84.02 est2029: parent 0,00 != sum(children) 20,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Instalare camere pietonal' vs 'TITLUL IV SUBVENTII'</t>
+          <t>84.02 total_2026: parent 32.673,00 != sum(children) 20,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>est2028</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Servicii dirigentie de santier pentru in' vs 'Titlul XII „Proiecte cu finanțare din su'</t>
+          <t>84.02 est2028: parent 0,00 != sum(children) 110,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>est2027</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Intretinere semafoare' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>84.02 est2027: parent 0,00 != sum(children) 10,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -29592,16 +29554,16 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (29%): 'Spor de putere scoala nr. 11 Tudor Vladi' vs 'Asigurari si asistenta sociala'</t>
+          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
@@ -29617,23 +29579,23 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (12%): 'Reparatii retea iluminat public b-dul 1 ' vs 'Excedent'</t>
+          <t>name mismatch vs nomenclator (51%): 'subvetie transport local' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -29642,16 +29604,16 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>98.02</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>duplicate of p12 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -29667,16 +29629,16 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>84.02.03.03</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (24%): 'Iluminat public in parcări nou infiintat' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>name mismatch vs nomenclator (32%): 'Strazi- S.P.Pavaje Spatii verzi' vs 'Strazi'</t>
         </is>
       </c>
     </row>
@@ -29692,16 +29654,16 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>duplicate of p13 with different values</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -29717,263 +29679,223 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'cheltuieli de capital din care:' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B309" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 0,00 != sum(children) 2.005,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'cheltuieli de capital (leasing)' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B310" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>trim3</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>74.02 trim3: parent 930,00 != sum(children) 170,00 (1 children)</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B311" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>84.02.03.03</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>74.02 trim1: parent 0,00 != sum(children) 10.700,00 (1 children)</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B312" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>trim4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>74.02 trim4: parent 678,00 != sum(children) 30,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (31%): 'Intretinere indicatoare rutiere' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B313" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>trim2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>74.02 trim2: parent 10.055,00 != sum(children) 1.105,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (36%): 'Indicatoare si stalpi de sustinere -pano' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (35%): 'Refacere suprafete deteriorate pe trotua' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>trim1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (35%): 'Achizitionare placute strazi si imobile' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>74.02.05.02</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>cell re-read from image (unverified transcription)</t>
+          <t>name mismatch vs nomenclator (36%): 'Intretinere placute strazi si imobile' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -29982,16 +29904,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (34%): 'cheltuieli de capital, din care:' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -30007,143 +29929,123 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'ENERGIE TERMICA' vs 'TITLUL IV SUBVENTII'</t>
+          <t>name mismatch vs nomenclator (30%): 'Achizitionare si montare oglinzi rutiere' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B319" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>est2028</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>84.02 est2028: parent 0,00 != sum(children) 110,00 (2 children)</t>
+          <t>duplicate of p8 with different values</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B320" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>84.02 total_2026: parent 32.673,00 != sum(children) 20,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (38%): 'Achizitionare si montare limitatoare de ' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B321" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>est2027</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>84.02 est2027: parent 0,00 != sum(children) 10,00 (2 children)</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>est2029</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>84.02 est2029: parent 0,00 != sum(children) 20,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (35%): 'Achizitionare si montare sisteme de ghid' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -30152,16 +30054,16 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -30177,23 +30079,23 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (51%): 'subvetie transport local' vs 'TITLUL IV SUBVENTII'</t>
+          <t>name mismatch vs nomenclator (21%): 'Supraveghere arheologica a obiectivelor ' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -30202,16 +30104,16 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -30227,16 +30129,16 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>84.02.03.03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Strazi- S.P.Pavaje Spatii verzi' vs 'Strazi'</t>
+          <t>name mismatch vs nomenclator (40%): 'Reparatii str. Stejarului, municipiul Ca' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -30252,11 +30154,11 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -30277,23 +30179,23 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'sume aferente persoanelor cu handicap ne' vs 'TITLUL XI ALTE CHELTUIELI'</t>
+          <t>name mismatch vs nomenclator (30%): 'Infiintare parcare aferenta bloc H1' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -30302,23 +30204,23 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'cheltuieli de capital (leasing)' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -30327,16 +30229,16 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>name mismatch vs nomenclator (20%): 'Achizitionare si montat indicatoare ruti' vs 'TITLUL III DOBANZI'</t>
         </is>
       </c>
     </row>
@@ -30352,16 +30254,16 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>84.02.03.03</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -30381,19 +30283,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Intretinere indicatoare rutiere' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>name mismatch vs nomenclator (35%): 'Achizitionare ,montare si intretinere pa' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -30411,7 +30313,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Indicatoare si stalpi de sustinere -pano' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -30436,14 +30338,14 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Refacere suprafete deteriorate pe trotua' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (29%): 'Servicii ridicare, transport si depozita' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -30456,12 +30358,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Achizitionare placute strazi si imobile' vs 'TITLUL III DOBANZI'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
@@ -30481,19 +30383,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Intretinere placute strazi si imobile' vs 'TITLUL IV SUBVENTII'</t>
+          <t>name mismatch vs nomenclator (32%): 'Servicii de coordonare in materie de sec' vs 'TITLUL V FONDURI DE REZERVA'</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -30506,19 +30408,19 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'Servicii medicale de medicina muncii' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -30531,19 +30433,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Achizitionare si montare oglinzi rutiere' vs 'Taxe pe servicii specifice'</t>
+          <t>duplicate of p16 with different values</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -30556,12 +30458,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>36.02</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>duplicate of p8 with different values</t>
+          <t>name mismatch vs nomenclator (28%): 'Amenajare trotuar str Petre Hanes , Zona' vs 'Diverse venituri'</t>
         </is>
       </c>
     </row>
@@ -30581,12 +30483,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'Achizitionare si montare limitatoare de ' vs 'TITLUL V FONDURI DE REZERVA'</t>
+          <t>name mismatch vs nomenclator (29%): 'Amenajare trotuar strada Petre Hanes' vs 'TITLUL IV SUBVENTII'</t>
         </is>
       </c>
     </row>
@@ -30606,12 +30508,12 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -30631,19 +30533,19 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'Achizitionare si montare sisteme de ghid' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
+          <t>name mismatch vs nomenclator (31%): 'Amenajare trotuar strada Av Aurel Elefte' vs 'TITLUL XXIII REZERVE, EXCEDENT/DEFICIT'</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -30656,12 +30558,12 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>name mismatch vs nomenclator (13%): 'Servicii de operare sistem de bike shari' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
         </is>
       </c>
     </row>
@@ -30681,12 +30583,12 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (21%): 'Supraveghere arheologica a obiectivelor ' vs 'TITLUL III DOBANZI'</t>
+          <t>name mismatch vs nomenclator (30%): 'Intretinere si reparatii curente strada ' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -30706,12 +30608,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>duplicate of p16 with different values</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30629,7 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30736,7 +30638,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (40%): 'Reparatii str. Stejarului, municipiul Ca' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>name mismatch vs nomenclator (31%): 'Amenajare sens giratoriu str.Prel.Sloboz' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -30752,7 +30654,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30760,506 +30662,6 @@
         </is>
       </c>
       <c r="F347" t="inlineStr">
-        <is>
-          <t>duplicate of p15 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>16</v>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (30%): 'Infiintare parcare aferenta bloc H1' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>16</v>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>duplicate of p15 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>16</v>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (20%): 'Achizitionare si montat indicatoare ruti' vs 'TITLUL III DOBANZI'</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>16</v>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>duplicate of p16 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>16</v>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (35%): 'Achizitionare ,montare si intretinere pa' vs 'TITLUL V FONDURI DE REZERVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>16</v>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>duplicate of p16 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>16</v>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (29%): 'Servicii ridicare, transport si depozita' vs 'TITLUL V FONDURI DE REZERVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>16</v>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>duplicate of p16 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>16</v>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (32%): 'Servicii de coordonare in materie de sec' vs 'TITLUL V FONDURI DE REZERVA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>16</v>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (32%): 'Servicii medicale de medicina muncii' vs '70.  CHELTUIELI DE CAPITAL (70=71+72+75)'</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>16</v>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>duplicate of p16 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>16</v>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>36.02</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (28%): 'Amenajare trotuar str Petre Hanes , Zona' vs 'Diverse venituri'</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>16</v>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (29%): 'Amenajare trotuar strada Petre Hanes' vs 'TITLUL IV SUBVENTII'</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>16</v>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>duplicate of p15 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>16</v>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (31%): 'Amenajare trotuar strada Av Aurel Elefte' vs 'TITLUL XXIII REZERVE, EXCEDENT/DEFICIT'</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>16</v>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (13%): 'Servicii de operare sistem de bike shari' vs 'TITLUL XIX ÎMPRUMUTURI'</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>16</v>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (30%): 'Intretinere si reparatii curente strada ' vs 'TITLUL II  BUNURI SI SERVICII'</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>16</v>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>duplicate of p15 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>17</v>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (31%): 'Amenajare sens giratoriu str.Prel.Sloboz' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>17</v>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
         <is>
           <t>duplicate of p15 with different values</t>
         </is>
@@ -31276,7 +30678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -31298,7 +30700,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -31308,72 +30710,230 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>286</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>56</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>327</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ca749df4b0c8b905e1861a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9f45afdfc5a5b68a5f39d4ceff59d1e4a92587b714bfdfef299a2a8e8d0ea2ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>— BUGETUL PROPRIU AL MUNICIPIULUI CALARASI PE ANUL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>unknown, pag. 1-17, 521 linii</t>
         </is>
